--- a/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-72</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>LCN047</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KCL-0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:25
@@ -126,7 +126,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm san TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">10:25
@@ -168,7 +168,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">13:55
@@ -182,7 +182,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi san, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">14:07
@@ -199,7 +199,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:33

--- a/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCL-0004</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:25
@@ -106,13 +106,10 @@
 12/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:37
@@ -154,9 +151,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:10
 12/03/2026</t>
   </si>
@@ -182,7 +176,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:07
@@ -1187,24 +1181,24 @@
         <v>9.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-2.807</v>
@@ -1222,24 +1216,24 @@
         <v>5.94</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-13.007</v>
@@ -1257,24 +1251,24 @@
         <v>6.24</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>42</v>
       </c>
       <c r="F14" s="15">
         <v>-18.207</v>
@@ -1292,24 +1286,24 @@
         <v>6.11</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>46</v>
       </c>
       <c r="F15" s="18">
         <v>-28.907</v>
@@ -1327,24 +1321,24 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>50</v>
       </c>
       <c r="F16" s="21">
         <v>-35.707</v>
@@ -1362,24 +1356,24 @@
         <v>15</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>52</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>54</v>
       </c>
       <c r="F17" s="24">
         <v>-38.207</v>
@@ -1397,24 +1391,24 @@
         <v>10.17</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F18" s="27">
         <v>-44.65</v>
@@ -1432,12 +1426,12 @@
         <v>3.03</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1543,31 +1537,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1607,7 +1601,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1636,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1665,7 +1659,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1694,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1723,7 +1717,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1752,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -1781,7 +1775,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" s="27">
         <v>1</v>
@@ -1804,13 +1798,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/6602988c-7f2b-4a12-85b9-f341aee481bc_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-72_D800_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">08:35
 12/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1181,24 +1184,24 @@
         <v>9.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-2.807</v>
@@ -1216,24 +1219,24 @@
         <v>5.94</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-13.007</v>
@@ -1251,24 +1254,24 @@
         <v>6.24</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="15">
         <v>-18.207</v>
@@ -1286,12 +1289,12 @@
         <v>6.11</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
@@ -1300,10 +1303,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" s="18">
         <v>-28.907</v>
@@ -1321,24 +1324,24 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="21">
         <v>-35.707</v>
@@ -1356,24 +1359,24 @@
         <v>15</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" s="24">
         <v>-38.207</v>
@@ -1391,24 +1394,24 @@
         <v>10.17</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="27">
         <v>-44.65</v>
@@ -1426,12 +1429,12 @@
         <v>3.03</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1537,31 +1540,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1601,7 +1604,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1630,7 +1633,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1659,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1717,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1746,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -1775,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="27">
         <v>1</v>
@@ -1798,13 +1801,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
